--- a/assets/docs/lop5/Toan - Lop 5.xlsx
+++ b/assets/docs/lop5/Toan - Lop 5.xlsx
@@ -1033,7 +1033,8 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Ở tiết luyện tập chung, GV cho HS làm bộ bài tập tương tác có chấm tự động về đọc, viết.</t>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở tiết luyện tập chung, GV cho HS làm bộ bài tập tương tác có chấm tự động về đọc, viết, so sánh và làm tròn số tự nhiên
+Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu bài toán thực tế có bảng số liệu, tô màu dòng cần dùng theo lời HS đọc đề; các em học cách lấy đúng số liệu</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1435,12 @@
           <t>30</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở tiết luyện tập chung, GV cho HS làm bộ câu hỏi tương tác có chấm tự động về đọc, viết, so sánh và làm tròn số thập phân
+Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu bảng hàng của số thập phân phóng to, bấm sáng dần từng hàng phần mười, phần trăm theo lời HS đọc số; nhờ nhìn rõ vị trí các hàng</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -1682,7 +1688,12 @@
           <t>38</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr"/>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở tiết luyện tập chung, GV cho HS làm bộ câu hỏi tương tác có chấm tự động về số thập phân và các phép tính đã học
+Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu bài toán thực tế có bảng số liệu, tô màu dòng và cột cần dùng theo lời HS đọc đề; các em học cách đọc bảng</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -2180,7 +2191,9 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>SGV 3 tiết; bớt 1 tiết cho kiểm tra định kì</t>
+          <t>SGV 3 tiết; bớt 1 tiết cho kiểm tra định kì
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở tiết luyện tập chung, GV cho HS làm bộ câu hỏi tương tác có chấm tự động; sau mỗi câu các em biết ngay đúng hay sai
+Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu bài toán thực tế có bảng số liệu, tô màu dòng và cột cần dùng theo lời HS đọc đề; các em học cách đọc bảng</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2708,8 @@
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Thực hành bài “Luyện tập chung”, GV chiếu các hình tam giác của bài 1 lên màn hình và.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Thực hành bài “Luyện tập chung”, GV chiếu các hình tam giác của bài 1 lên màn hình và vẽ dần đường cao ứng với đáy BC, EG, IK
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần tính diện tích, chu vi, GV mở bảng tính có sẵn công thức: HS tự tính ra vở trước rồi nhập số đo vào bảng</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3781,8 @@
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Khởi động bài “Luyện tập”, GV chiếu bài toán mua tám chiếc vòng lên màn hình.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Khởi động bài “Luyện tập”, GV chiếu bài toán mua tám chiếc vòng lên màn hình cùng bảng giá
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở hoạt động Thực hành, GV mở bảng tính có sẵn công thức: HS tính ra vở trước rồi nhập số lượng và đơn giá để máy hiện tổng tiền</t>
         </is>
       </c>
     </row>
@@ -3987,7 +4002,12 @@
           <t>113</t>
         </is>
       </c>
-      <c r="H116" s="4" t="inlineStr"/>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Khởi động bài “Luyện tập chung”, GV chiếu các hình và số liệu của bài lên màn hình
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Thực hành, GV mở bảng tính có sẵn công thức: HS tính ra vở trước rồi nhập số đo để đối chiếu; khi kết quả lệch nhau</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -4426,7 +4446,9 @@
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>SGV 3 tiết; bớt 1 tiết cho kiểm tra định kì</t>
+          <t>SGV 3 tiết; bớt 1 tiết cho kiểm tra định kì
+Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Khởi động bài “Luyện tập chung”, GV chiếu các hình cần quan sát lên màn hình, xoay và tô màu từng mặt để HS nhận ra hình khối
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Thực hành, GV mở bảng tính có sẵn công thức: HS tính ra vở trước rồi nhập số đo để đối chiếu; khi kết quả lệch nhau</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4952,12 @@
           <t>143</t>
         </is>
       </c>
-      <c r="H146" s="4" t="inlineStr"/>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Khởi động bài “Luyện tập chung”, GV chiếu các hình và số liệu của bài lên màn hình
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Thực hành, GV mở bảng tính có sẵn công thức: HS tính ra vở trước rồi nhập số đo để đối chiếu; khi kết quả lệch nhau</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -5210,7 +5237,8 @@
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Khởi động bài “Luyện tập chung”, GV chiếu các hình và số liệu của bài lên màn hình, tô.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Khởi động bài “Luyện tập chung”, GV chiếu các hình và số liệu của bài lên màn hình
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Thực hành, GV mở bảng tính có sẵn công thức: HS tính ra vở trước rồi nhập số đo để đối chiếu; khi kết quả lệch nhau</t>
         </is>
       </c>
     </row>
